--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92575808604</v>
+        <v>46157.93120930922</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93120930922</v>
+        <v>46157.93186587723</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93186587723</v>
+        <v>46157.93407169489</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93407169489</v>
+        <v>46157.93725322919</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93725322919</v>
+        <v>46158.28222809899</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28222809899</v>
+        <v>46158.29711509468</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29711509468</v>
+        <v>46158.29822878178</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29822878178</v>
+        <v>46158.33393806035</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33393806035</v>
+        <v>46158.36863560558</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Медведев- соц. работник/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36863560558</v>
+        <v>46158.37294562373</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
